--- a/Arquivos/AULA 07.10.2026 METODO DE TRANSPORTE.xlsx
+++ b/Arquivos/AULA 07.10.2026 METODO DE TRANSPORTE.xlsx
@@ -8,44 +8,75 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58349D12-6A0D-457D-9CB1-C414D8BB6FF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99D7C52-BE0A-4073-991A-AB80FC6B5089}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{DE9075F5-B8F8-4415-82B8-3ED555B11A03}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Ex2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'Ex 1'!$B$2:$G$2</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">'Ex2'!$B$2:$J$2</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Ex 1'!$H$7:$H$11</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'Ex2'!$K$7:$K$12</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'Ex 1'!$H$4</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">'Ex2'!$B$4</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'Ex 1'!$I$7:$I$11</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'Ex2'!$L$7:$L$12</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
   <si>
     <t>CUSTO</t>
   </si>
@@ -114,13 +145,55 @@
   </si>
   <si>
     <t>Função Objetivo</t>
+  </si>
+  <si>
+    <t>RESTRIÇÕES</t>
+  </si>
+  <si>
+    <t>X31</t>
+  </si>
+  <si>
+    <t>x32</t>
+  </si>
+  <si>
+    <t>x33</t>
+  </si>
+  <si>
+    <t>custo</t>
+  </si>
+  <si>
+    <t>função</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>USADO</t>
+  </si>
+  <si>
+    <t>DISPONIVEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,8 +201,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,8 +223,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -151,18 +238,126 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -207,6 +402,48 @@
       <calculatedColumnFormula>SUMPRODUCT(B7:G7,$B$2:$G$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{7D45E1E7-F425-460D-93FF-529D980A419F}" name="disponivel"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FB41A2DE-C93C-4ABC-A8BD-7FF6D167CB5D}" name="Tabela4" displayName="Tabela4" ref="A1:J4" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:J4" xr:uid="{BE74B2B7-6379-48E2-8BC5-B1D74D225935}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{A77841BA-D7CD-4983-8585-E8149E21A411}" name="Coluna1"/>
+    <tableColumn id="2" xr3:uid="{A0D1766C-96C3-48F2-B660-5AF39FC9603B}" name="x11"/>
+    <tableColumn id="3" xr3:uid="{7FF31712-B234-4A3F-B025-5201BCEB6D8E}" name="x12"/>
+    <tableColumn id="4" xr3:uid="{7F460268-9664-47B2-81BD-0A3009F83963}" name="x13"/>
+    <tableColumn id="5" xr3:uid="{2E0450E3-9808-4E02-A497-9350C7F7ED61}" name="x21"/>
+    <tableColumn id="6" xr3:uid="{CEAB1B01-B699-44D6-B397-71C771798E0F}" name="x22"/>
+    <tableColumn id="7" xr3:uid="{FC09B688-0A45-4F6F-8AE2-48FC243A7FFA}" name="x23"/>
+    <tableColumn id="8" xr3:uid="{87A71876-FE6E-4B6A-9228-AB8D7EFB4BFC}" name="X31"/>
+    <tableColumn id="9" xr3:uid="{332AEC9E-F31F-4FFB-917B-8B8B6D8C5903}" name="x32"/>
+    <tableColumn id="10" xr3:uid="{6841B98C-C5CA-49E9-9259-A69D1860E007}" name="x33"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{866B94D6-D3C9-4096-BEA2-375AEB30C113}" name="Tabela5" displayName="Tabela5" ref="A6:L12" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A6:L12" xr:uid="{996849BB-B066-4A6D-9F13-BCEC35C6836D}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{9DC5CEBB-6308-4640-B721-06590C9FD98E}" name="RESTRIÇÕES"/>
+    <tableColumn id="2" xr3:uid="{609505CB-3C67-47CD-B68E-59FA32F8765F}" name="x11"/>
+    <tableColumn id="3" xr3:uid="{94FC6FFB-340D-4AE0-943A-31539DFF60CB}" name="x12"/>
+    <tableColumn id="4" xr3:uid="{11D98E2F-877E-4824-A841-E1DEF51F009D}" name="x13"/>
+    <tableColumn id="5" xr3:uid="{99E74DE4-A633-4143-89A7-CA36C41605E8}" name="x21"/>
+    <tableColumn id="6" xr3:uid="{E6CF7B29-4E39-4E63-8796-3EB89B09A12C}" name="x22"/>
+    <tableColumn id="7" xr3:uid="{90E6752C-8C19-4662-8A90-A714A54BFFCB}" name="x23"/>
+    <tableColumn id="8" xr3:uid="{2BAABE20-9904-449C-A87B-5A1A06F33E02}" name="X31"/>
+    <tableColumn id="9" xr3:uid="{6F211DF6-4723-489E-B6CC-A8CE9DFCFDBB}" name="x32"/>
+    <tableColumn id="10" xr3:uid="{61462865-AB7D-459A-9964-A936A08D3BC0}" name="x33"/>
+    <tableColumn id="11" xr3:uid="{EC8BA602-9ACD-4FF7-A661-A0CC94DD1C9F}" name="USADO">
+      <calculatedColumnFormula>SUMPRODUCT(B7:J7,$B$2:$J$2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{7CBF921B-7F04-4083-A998-F29B39B14C8A}" name="DISPONIVEL"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -730,4 +967,289 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CAA59F-4004-442D-A909-BD412ADA6F83}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>57</v>
+      </c>
+      <c r="E2">
+        <v>41</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>80</v>
+      </c>
+      <c r="J2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>8</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <f>SUMPRODUCT(B3:J3,B2:J2)</f>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <f>SUMPRODUCT(B7:J7,$B$2:$J$2)</f>
+        <v>57</v>
+      </c>
+      <c r="L7">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <f t="shared" ref="K8:K12" si="0">SUMPRODUCT(B8:J8,$B$2:$J$2)</f>
+        <v>76</v>
+      </c>
+      <c r="L8">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="L9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="L10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="L11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="L12">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Arquivos/AULA 07.10.2026 METODO DE TRANSPORTE.xlsx
+++ b/Arquivos/AULA 07.10.2026 METODO DE TRANSPORTE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99D7C52-BE0A-4073-991A-AB80FC6B5089}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C205032F-57EF-4A52-A58B-4B316FE533B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{DE9075F5-B8F8-4415-82B8-3ED555B11A03}"/>
   </bookViews>

--- a/Arquivos/AULA 07.10.2026 METODO DE TRANSPORTE.xlsx
+++ b/Arquivos/AULA 07.10.2026 METODO DE TRANSPORTE.xlsx
@@ -8,75 +8,109 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C205032F-57EF-4A52-A58B-4B316FE533B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76524B76-CA02-4A30-BCDE-76F79D7B67FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{DE9075F5-B8F8-4415-82B8-3ED555B11A03}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{DE9075F5-B8F8-4415-82B8-3ED555B11A03}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex 1" sheetId="1" r:id="rId1"/>
     <sheet name="Ex2" sheetId="2" r:id="rId2"/>
+    <sheet name="Ex3)" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'Ex 1'!$B$2:$G$2</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">'Ex2'!$B$2:$J$2</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'Ex3)'!$B$2:$P$2</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Ex 1'!$H$7:$H$11</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">'Ex2'!$K$7:$K$12</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'Ex3)'!$Q$12:$Q$14</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'Ex3)'!$Q$7:$Q$11</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'Ex 1'!$H$4</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">'Ex2'!$B$4</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'Ex3)'!$B$4</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'Ex 1'!$I$7:$I$11</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">'Ex2'!$L$7:$L$12</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'Ex3)'!$R$12:$R$14</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">'Ex3)'!$R$7:$R$11</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
   <si>
     <t>CUSTO</t>
   </si>
@@ -187,6 +221,48 @@
   </si>
   <si>
     <t>DISPONIVEL</t>
+  </si>
+  <si>
+    <t>x41</t>
+  </si>
+  <si>
+    <t>x42</t>
+  </si>
+  <si>
+    <t>x43</t>
+  </si>
+  <si>
+    <t>x51</t>
+  </si>
+  <si>
+    <t>x52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>f1</t>
+  </si>
+  <si>
+    <t>f3</t>
+  </si>
+  <si>
+    <t>f2</t>
+  </si>
+  <si>
+    <t>f4</t>
+  </si>
+  <si>
+    <t>f5</t>
+  </si>
+  <si>
+    <t>CD1</t>
+  </si>
+  <si>
+    <t>CD2</t>
+  </si>
+  <si>
+    <t>CD3</t>
   </si>
 </sst>
 </file>
@@ -210,7 +286,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,8 +305,14 @@
         <bgColor theme="4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -282,11 +364,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -294,11 +394,73 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -408,7 +570,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FB41A2DE-C93C-4ABC-A8BD-7FF6D167CB5D}" name="Tabela4" displayName="Tabela4" ref="A1:J4" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FB41A2DE-C93C-4ABC-A8BD-7FF6D167CB5D}" name="Tabela4" displayName="Tabela4" ref="A1:J4" totalsRowShown="0" headerRowDxfId="3">
   <autoFilter ref="A1:J4" xr:uid="{BE74B2B7-6379-48E2-8BC5-B1D74D225935}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{A77841BA-D7CD-4983-8585-E8149E21A411}" name="Coluna1"/>
@@ -427,7 +589,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{866B94D6-D3C9-4096-BEA2-375AEB30C113}" name="Tabela5" displayName="Tabela5" ref="A6:L12" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{866B94D6-D3C9-4096-BEA2-375AEB30C113}" name="Tabela5" displayName="Tabela5" ref="A6:L12" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A6:L12" xr:uid="{996849BB-B066-4A6D-9F13-BCEC35C6836D}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{9DC5CEBB-6308-4640-B721-06590C9FD98E}" name="RESTRIÇÕES"/>
@@ -444,6 +606,56 @@
       <calculatedColumnFormula>SUMPRODUCT(B7:J7,$B$2:$J$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{7CBF921B-7F04-4083-A998-F29B39B14C8A}" name="DISPONIVEL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CFEFF7A0-6B54-4F7D-A50D-5016190AB9E2}" name="Tabela43" displayName="Tabela43" ref="A1:P4" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:P4" xr:uid="{BE74B2B7-6379-48E2-8BC5-B1D74D225935}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{DF3F0ACA-F9B0-41BE-AB15-B849A3FC8C96}" name="Coluna1"/>
+    <tableColumn id="2" xr3:uid="{F95D7EB9-39FA-46DA-8492-8B7172820C20}" name="x11"/>
+    <tableColumn id="3" xr3:uid="{A1708E7D-383F-4297-874C-DDA6DE7F85D6}" name="x12"/>
+    <tableColumn id="4" xr3:uid="{F8C9914D-563E-47D9-98A8-626F4C349A8C}" name="x13"/>
+    <tableColumn id="5" xr3:uid="{47A0D3CD-39C0-4705-8F97-DE09A641542C}" name="x21"/>
+    <tableColumn id="6" xr3:uid="{C6B40CCB-3C67-4CE3-9C17-FA05933C88AA}" name="x22"/>
+    <tableColumn id="7" xr3:uid="{455A0651-8156-4579-AC6A-3901173392BE}" name="x23"/>
+    <tableColumn id="8" xr3:uid="{F9502F70-4DEE-469C-9BD4-2697E596DFC5}" name="X31"/>
+    <tableColumn id="9" xr3:uid="{AD75064D-AE96-4B79-95B3-AABDC694B6C2}" name="x32"/>
+    <tableColumn id="10" xr3:uid="{3CEF5491-6BAE-426E-8E8E-8380D3C3E746}" name="x33"/>
+    <tableColumn id="11" xr3:uid="{BFB92A00-2385-49BF-B6DA-CF9DF63F9C87}" name="x41"/>
+    <tableColumn id="12" xr3:uid="{507B6289-5B5A-47C5-85AB-9D32C56301AE}" name="x42"/>
+    <tableColumn id="13" xr3:uid="{C3C5CF84-675C-4795-91A3-CABE45AF7BA9}" name="x43"/>
+    <tableColumn id="15" xr3:uid="{DDFEAC7B-6873-41A3-A7B9-AE440E753E23}" name="x51"/>
+    <tableColumn id="16" xr3:uid="{10C35017-2893-41BE-ACEA-3B4043BBE712}" name="x52"/>
+    <tableColumn id="17" xr3:uid="{EA0A6E3C-4EE5-42F9-8B10-8B10C430BE53}" name="53"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4C7E7F9E-BD40-47B4-BBCD-1DEB1F20DD95}" name="Tabela57" displayName="Tabela57" ref="A6:P14" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A6:P14" xr:uid="{996849BB-B066-4A6D-9F13-BCEC35C6836D}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{3198886F-B3D9-4AB5-972D-2B1B9A0DD5A3}" name="RESTRIÇÕES"/>
+    <tableColumn id="2" xr3:uid="{B5F02E3A-39D5-4468-B9A3-9EECB2A597D8}" name="x11"/>
+    <tableColumn id="3" xr3:uid="{04195727-8620-4B95-BD5A-B997E6F728B0}" name="x12"/>
+    <tableColumn id="4" xr3:uid="{89B00FFB-CF3E-4982-BF3B-B7BF1EEEB93F}" name="x13"/>
+    <tableColumn id="5" xr3:uid="{C56C3880-EC6C-4C47-88FC-2E6548B90508}" name="x21"/>
+    <tableColumn id="6" xr3:uid="{7C69FFB2-4AE1-443A-B443-0ABC1A83298C}" name="x22"/>
+    <tableColumn id="7" xr3:uid="{2B8E6F9A-872F-4AA9-9089-378FB093AE42}" name="x23"/>
+    <tableColumn id="8" xr3:uid="{C06D9C45-B23D-43C1-A76C-34C598F24EA2}" name="X31"/>
+    <tableColumn id="9" xr3:uid="{0FB539D3-1514-4D58-8116-8AF4925ACC29}" name="x32"/>
+    <tableColumn id="10" xr3:uid="{3587D693-C964-471B-87FB-3C8FF82546AD}" name="x33"/>
+    <tableColumn id="11" xr3:uid="{1B9C9C78-0365-4962-B04C-0C20996A24DD}" name="x41"/>
+    <tableColumn id="12" xr3:uid="{C5A0A57D-80EA-4478-9B03-5517002F79FB}" name="x42"/>
+    <tableColumn id="13" xr3:uid="{78F03F60-ABDB-4AF8-ABB6-C3B94033B7A8}" name="x43"/>
+    <tableColumn id="14" xr3:uid="{F1A0F686-1A97-4AD5-86C0-C8894CAD1657}" name="x51"/>
+    <tableColumn id="15" xr3:uid="{A310F55D-3799-4411-81C0-075956841F14}" name="x52"/>
+    <tableColumn id="16" xr3:uid="{0F65534D-1C02-459F-A4AF-85A8EF178335}" name="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1252,4 +1464,410 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{881C3257-9A44-4577-A827-8399798A8DA3}">
+  <dimension ref="A1:R14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3000</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>3000</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2000</v>
+      </c>
+      <c r="O2">
+        <v>3000</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3">
+        <v>90</v>
+      </c>
+      <c r="C3">
+        <v>62</v>
+      </c>
+      <c r="D3">
+        <v>76</v>
+      </c>
+      <c r="E3">
+        <v>82</v>
+      </c>
+      <c r="F3">
+        <v>58</v>
+      </c>
+      <c r="G3">
+        <v>70</v>
+      </c>
+      <c r="H3">
+        <v>92</v>
+      </c>
+      <c r="I3">
+        <v>64</v>
+      </c>
+      <c r="J3">
+        <v>80</v>
+      </c>
+      <c r="K3">
+        <v>84</v>
+      </c>
+      <c r="L3">
+        <v>56</v>
+      </c>
+      <c r="N3">
+        <v>86</v>
+      </c>
+      <c r="O3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <f>SUMPRODUCT(B3:P3,B2:P2)</f>
+        <v>884000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="7">
+        <f>SUMPRODUCT(B7:P7,$B$2:$P$2)</f>
+        <v>1000</v>
+      </c>
+      <c r="R7">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="7">
+        <f t="shared" ref="Q8:Q14" si="0">SUMPRODUCT(B8:P8,$B$2:$P$2)</f>
+        <v>3000</v>
+      </c>
+      <c r="R8">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="7">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="R10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="7">
+        <f>SUMPRODUCT(B11:P11,$B$2:$P$2)</f>
+        <v>5000</v>
+      </c>
+      <c r="R11">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="7">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="R12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="R13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="7">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="R14">
+        <v>4000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Arquivos/AULA 07.10.2026 METODO DE TRANSPORTE.xlsx
+++ b/Arquivos/AULA 07.10.2026 METODO DE TRANSPORTE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76524B76-CA02-4A30-BCDE-76F79D7B67FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77C242D-BCB4-45A0-98EA-CBE4A95952F6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{DE9075F5-B8F8-4415-82B8-3ED555B11A03}"/>
   </bookViews>
@@ -269,7 +269,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +284,13 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -383,10 +393,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -398,8 +409,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -1472,6 +1485,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5703125" customWidth="1"/>
     <col min="12" max="12" width="13.7109375" customWidth="1"/>
     <col min="18" max="18" width="13.7109375" customWidth="1"/>
@@ -1622,7 +1636,7 @@
       <c r="A4" t="s">
         <v>24</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="11">
         <f>SUMPRODUCT(B3:P3,B2:P2)</f>
         <v>884000</v>
       </c>
